--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J524"/>
+  <dimension ref="A1:J529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19300,6 +19300,186 @@
         <v>369.99</v>
       </c>
       <c r="J524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="C525" t="n">
+        <v>359.18</v>
+      </c>
+      <c r="D525" t="n">
+        <v>360.15</v>
+      </c>
+      <c r="E525" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="F525" t="n">
+        <v>352.63</v>
+      </c>
+      <c r="G525" t="n">
+        <v>359.37</v>
+      </c>
+      <c r="H525" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="I525" t="n">
+        <v>369.99</v>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="C526" t="n">
+        <v>359.62</v>
+      </c>
+      <c r="D526" t="n">
+        <v>360.93</v>
+      </c>
+      <c r="E526" t="n">
+        <v>355.53</v>
+      </c>
+      <c r="F526" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="G526" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="H526" t="n">
+        <v>365.11</v>
+      </c>
+      <c r="I526" t="n">
+        <v>370.31</v>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="C527" t="n">
+        <v>359.59</v>
+      </c>
+      <c r="D527" t="n">
+        <v>361.09</v>
+      </c>
+      <c r="E527" t="n">
+        <v>355.72</v>
+      </c>
+      <c r="F527" t="n">
+        <v>354.19</v>
+      </c>
+      <c r="G527" t="n">
+        <v>361.41</v>
+      </c>
+      <c r="H527" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="I527" t="n">
+        <v>369.77</v>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="C528" t="n">
+        <v>360.02</v>
+      </c>
+      <c r="D528" t="n">
+        <v>361.14</v>
+      </c>
+      <c r="E528" t="n">
+        <v>356.07</v>
+      </c>
+      <c r="F528" t="n">
+        <v>354.73</v>
+      </c>
+      <c r="G528" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="H528" t="n">
+        <v>365.07</v>
+      </c>
+      <c r="I528" t="n">
+        <v>369.82</v>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>372.31</v>
+      </c>
+      <c r="C529" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="D529" t="n">
+        <v>361.44</v>
+      </c>
+      <c r="E529" t="n">
+        <v>356.32</v>
+      </c>
+      <c r="F529" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="G529" t="n">
+        <v>363.68</v>
+      </c>
+      <c r="H529" t="n">
+        <v>365.59</v>
+      </c>
+      <c r="I529" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="J529" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19316,7 +19496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B645"/>
+  <dimension ref="A1:B651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25769,6 +25949,66 @@
       </c>
       <c r="B645" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -25937,28 +26177,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3058907900457652</v>
+        <v>-0.3089462240784354</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K2" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05547802478129393</v>
+        <v>0.05750710273083048</v>
       </c>
       <c r="M2" t="n">
-        <v>7.500154566636297</v>
+        <v>7.443906712523604</v>
       </c>
       <c r="N2" t="n">
-        <v>84.27908538784291</v>
+        <v>83.52389341890063</v>
       </c>
       <c r="O2" t="n">
-        <v>9.180364120656812</v>
+        <v>9.139140737449042</v>
       </c>
       <c r="P2" t="n">
-        <v>380.8783502427693</v>
+        <v>380.9133419590345</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26015,28 +26255,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3602633969197191</v>
+        <v>-0.3864570351838585</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K3" t="n">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06354428609387031</v>
+        <v>0.07240653962245158</v>
       </c>
       <c r="M3" t="n">
-        <v>8.159117398313905</v>
+        <v>8.213224777506246</v>
       </c>
       <c r="N3" t="n">
-        <v>100.3815575116134</v>
+        <v>101.3444636234085</v>
       </c>
       <c r="O3" t="n">
-        <v>10.01905971194969</v>
+        <v>10.06699873961493</v>
       </c>
       <c r="P3" t="n">
-        <v>383.8150119970245</v>
+        <v>384.1167504889499</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26093,28 +26333,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2903949387828526</v>
+        <v>-0.3161990439752259</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K4" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0554161717015097</v>
+        <v>0.0646618510009237</v>
       </c>
       <c r="M4" t="n">
-        <v>7.349722373532224</v>
+        <v>7.417468808141555</v>
       </c>
       <c r="N4" t="n">
-        <v>76.6582308784655</v>
+        <v>77.83745514307701</v>
       </c>
       <c r="O4" t="n">
-        <v>8.755468627004811</v>
+        <v>8.822553776717772</v>
       </c>
       <c r="P4" t="n">
-        <v>383.1320745708476</v>
+        <v>383.4263722324087</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26171,28 +26411,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3754702921167387</v>
+        <v>-0.3965524349549149</v>
       </c>
       <c r="J5" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K5" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09485289933552787</v>
+        <v>0.1047426526629868</v>
       </c>
       <c r="M5" t="n">
-        <v>7.042333707363329</v>
+        <v>7.086962582845467</v>
       </c>
       <c r="N5" t="n">
-        <v>71.74579234618672</v>
+        <v>72.3390123967672</v>
       </c>
       <c r="O5" t="n">
-        <v>8.470288799455821</v>
+        <v>8.505234411629536</v>
       </c>
       <c r="P5" t="n">
-        <v>377.5650251369124</v>
+        <v>377.8054657889627</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26249,28 +26489,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3629530471747482</v>
+        <v>-0.3842664098759168</v>
       </c>
       <c r="J6" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K6" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1307831341876901</v>
+        <v>0.1431749893495291</v>
       </c>
       <c r="M6" t="n">
-        <v>5.750483230626646</v>
+        <v>5.825700918918947</v>
       </c>
       <c r="N6" t="n">
-        <v>46.69324085698125</v>
+        <v>47.55945061743575</v>
       </c>
       <c r="O6" t="n">
-        <v>6.833245265390468</v>
+        <v>6.896336028460022</v>
       </c>
       <c r="P6" t="n">
-        <v>375.7162195795291</v>
+        <v>375.959284019335</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26327,28 +26567,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4310234539612559</v>
+        <v>-0.4502322101318619</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K7" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1679088853628604</v>
+        <v>0.179971874864761</v>
       </c>
       <c r="M7" t="n">
-        <v>5.750184102510695</v>
+        <v>5.80696522169699</v>
       </c>
       <c r="N7" t="n">
-        <v>49.09934880645952</v>
+        <v>49.71005439540608</v>
       </c>
       <c r="O7" t="n">
-        <v>7.007092749954115</v>
+        <v>7.050535752367055</v>
       </c>
       <c r="P7" t="n">
-        <v>383.8322297280693</v>
+        <v>384.0512783109327</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26405,28 +26645,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2956981023602386</v>
+        <v>-0.3133891890793007</v>
       </c>
       <c r="J8" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K8" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06456496860660987</v>
+        <v>0.07230861111105269</v>
       </c>
       <c r="M8" t="n">
-        <v>6.770010391392261</v>
+        <v>6.803656745341426</v>
       </c>
       <c r="N8" t="n">
-        <v>67.56013076166884</v>
+        <v>67.81543233351071</v>
       </c>
       <c r="O8" t="n">
-        <v>8.219496989577211</v>
+        <v>8.235012588545978</v>
       </c>
       <c r="P8" t="n">
-        <v>383.1032882714499</v>
+        <v>383.3050665752819</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26483,28 +26723,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2729740225507806</v>
+        <v>-0.289430007186334</v>
       </c>
       <c r="J9" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K9" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0554350481649436</v>
+        <v>0.06231218768826685</v>
       </c>
       <c r="M9" t="n">
-        <v>6.611099561290213</v>
+        <v>6.648903010581512</v>
       </c>
       <c r="N9" t="n">
-        <v>67.71217401601423</v>
+        <v>67.84524123979514</v>
       </c>
       <c r="O9" t="n">
-        <v>8.22874073087822</v>
+        <v>8.23682227802659</v>
       </c>
       <c r="P9" t="n">
-        <v>386.5018952641889</v>
+        <v>386.6895849392336</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26542,7 +26782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J524"/>
+  <dimension ref="A1:J529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53781,6 +54021,266 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-45.76171540082111,170.66615081495266</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-45.76206050296065,170.66687611451968</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-45.762229602493996,170.66769814113857</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-45.76236905830649,170.6685544454017</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-45.762488287408196,170.66943936340473</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-45.762554268655876,170.67033209251514</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-45.762571389332756,170.67120855124165</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-45.76254618179221,170.67209008073937</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-45.761687048902296,170.66617210528452</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-45.76205686360759,170.66687834008027</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-45.76222280400382,170.66770062767708</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-45.76236418668861,170.66855568597686</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-45.76248149746716,170.66944132784502</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-45.76254135116303,170.6703354994572</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-45.762576226688836,170.6712079054284</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-45.76254330550328,170.6720902614971</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-45.761693260839955,170.66616744055077</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-45.762057111745285,170.6668781883375</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-45.76222140944172,170.6677011377362</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-45.76236250376605,170.66855611453911</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-45.76247453116396,170.66944334330915</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-45.762536219556225,170.67033685289948</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-45.76257667459217,170.67120784563085</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-45.76254815924085,170.67208995646837</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-45.76169565004669,170.66616564642212</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-45.76205355510476,170.66688036331692</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-45.762220973641064,170.66770129712964</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-45.76235940364554,170.66855690399584</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-45.76246976938705,170.6694447209679</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-45.762527460434235,170.6703391630848</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-45.7625765850115,170.67120785759036</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-45.762547709820716,170.67208998471176</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-45.76168442077477,170.6661740788254</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-45.762051652715606,170.66688152667788</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-45.76221835883712,170.66770225349038</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-45.76235718927375,170.66855746789344</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-45.76246324398904,170.6694466088702</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-45.762516135508704,170.67034214998995</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-45.76257192681678,170.67120847948462</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-45.76254528295191,170.67209013722618</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J529"/>
+  <dimension ref="A1:J532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19480,6 +19480,114 @@
         <v>370.09</v>
       </c>
       <c r="J529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>372.31</v>
+      </c>
+      <c r="C530" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="D530" t="n">
+        <v>361.44</v>
+      </c>
+      <c r="E530" t="n">
+        <v>356.32</v>
+      </c>
+      <c r="F530" t="n">
+        <v>355.68</v>
+      </c>
+      <c r="G530" t="n">
+        <v>364.22</v>
+      </c>
+      <c r="H530" t="n">
+        <v>365.34</v>
+      </c>
+      <c r="I530" t="n">
+        <v>369.06</v>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="C531" t="n">
+        <v>360.19</v>
+      </c>
+      <c r="D531" t="n">
+        <v>361.12</v>
+      </c>
+      <c r="E531" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="F531" t="n">
+        <v>355.72</v>
+      </c>
+      <c r="G531" t="n">
+        <v>364.61</v>
+      </c>
+      <c r="H531" t="n">
+        <v>365.74</v>
+      </c>
+      <c r="I531" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="C532" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="D532" t="n">
+        <v>360.91</v>
+      </c>
+      <c r="E532" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="F532" t="n">
+        <v>356.03</v>
+      </c>
+      <c r="G532" t="n">
+        <v>364.8</v>
+      </c>
+      <c r="H532" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="I532" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="J532" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19496,7 +19604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B651"/>
+  <dimension ref="A1:B654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26009,6 +26117,36 @@
       </c>
       <c r="B651" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -26177,28 +26315,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3089462240784354</v>
+        <v>-0.3086318141584496</v>
       </c>
       <c r="J2" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K2" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05750710273083048</v>
+        <v>0.05799787778684773</v>
       </c>
       <c r="M2" t="n">
-        <v>7.443906712523604</v>
+        <v>7.404630851030439</v>
       </c>
       <c r="N2" t="n">
-        <v>83.52389341890063</v>
+        <v>83.05255138840413</v>
       </c>
       <c r="O2" t="n">
-        <v>9.139140737449042</v>
+        <v>9.113317254897041</v>
       </c>
       <c r="P2" t="n">
-        <v>380.9133419590345</v>
+        <v>380.9097182835694</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26255,28 +26393,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3864570351838585</v>
+        <v>-0.4009600699011798</v>
       </c>
       <c r="J3" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K3" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07240653962245158</v>
+        <v>0.07760080992450691</v>
       </c>
       <c r="M3" t="n">
-        <v>8.213224777506246</v>
+        <v>8.241406581912658</v>
       </c>
       <c r="N3" t="n">
-        <v>101.3444636234085</v>
+        <v>101.7721962750595</v>
       </c>
       <c r="O3" t="n">
-        <v>10.06699873961493</v>
+        <v>10.08822066942727</v>
       </c>
       <c r="P3" t="n">
-        <v>384.1167504889499</v>
+        <v>384.2844094636377</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26333,28 +26471,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3161990439752259</v>
+        <v>-0.3308702991059165</v>
       </c>
       <c r="J4" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K4" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0646618510009237</v>
+        <v>0.07020974868871743</v>
       </c>
       <c r="M4" t="n">
-        <v>7.417468808141555</v>
+        <v>7.452695289735246</v>
       </c>
       <c r="N4" t="n">
-        <v>77.83745514307701</v>
+        <v>78.44778725768465</v>
       </c>
       <c r="O4" t="n">
-        <v>8.822553776717772</v>
+        <v>8.857075547701095</v>
       </c>
       <c r="P4" t="n">
-        <v>383.4263722324087</v>
+        <v>383.5943039324908</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26411,28 +26549,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3965524349549149</v>
+        <v>-0.4081594596218151</v>
       </c>
       <c r="J5" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K5" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1047426526629868</v>
+        <v>0.110468107927064</v>
       </c>
       <c r="M5" t="n">
-        <v>7.086962582845467</v>
+        <v>7.10841551002702</v>
       </c>
       <c r="N5" t="n">
-        <v>72.3390123967672</v>
+        <v>72.58751027218324</v>
       </c>
       <c r="O5" t="n">
-        <v>8.505234411629536</v>
+        <v>8.519830413346456</v>
       </c>
       <c r="P5" t="n">
-        <v>377.8054657889627</v>
+        <v>377.938321618187</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26489,28 +26627,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3842664098759168</v>
+        <v>-0.3947118192709023</v>
       </c>
       <c r="J6" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K6" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1431749893495291</v>
+        <v>0.1498612922848476</v>
       </c>
       <c r="M6" t="n">
-        <v>5.825700918918947</v>
+        <v>5.855925707018542</v>
       </c>
       <c r="N6" t="n">
-        <v>47.55945061743575</v>
+        <v>47.82314570337383</v>
       </c>
       <c r="O6" t="n">
-        <v>6.896336028460022</v>
+        <v>6.915428092560418</v>
       </c>
       <c r="P6" t="n">
-        <v>375.959284019335</v>
+        <v>376.0788413029807</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26567,28 +26705,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4502322101318619</v>
+        <v>-0.4580995249923026</v>
       </c>
       <c r="J7" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K7" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L7" t="n">
-        <v>0.179971874864761</v>
+        <v>0.1858873330477346</v>
       </c>
       <c r="M7" t="n">
-        <v>5.80696522169699</v>
+        <v>5.819278971883649</v>
       </c>
       <c r="N7" t="n">
-        <v>49.71005439540608</v>
+        <v>49.7315458034011</v>
       </c>
       <c r="O7" t="n">
-        <v>7.050535752367055</v>
+        <v>7.052059685184259</v>
       </c>
       <c r="P7" t="n">
-        <v>384.0512783109327</v>
+        <v>384.1413241788422</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26645,28 +26783,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3133891890793007</v>
+        <v>-0.3231619373083853</v>
       </c>
       <c r="J8" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K8" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07230861111105269</v>
+        <v>0.07683119514958681</v>
       </c>
       <c r="M8" t="n">
-        <v>6.803656745341426</v>
+        <v>6.820268416763935</v>
       </c>
       <c r="N8" t="n">
-        <v>67.81543233351071</v>
+        <v>67.89870604064454</v>
       </c>
       <c r="O8" t="n">
-        <v>8.235012588545978</v>
+        <v>8.240067113843462</v>
       </c>
       <c r="P8" t="n">
-        <v>383.3050665752819</v>
+        <v>383.4169218166301</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26723,28 +26861,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.289430007186334</v>
+        <v>-0.3001501282153313</v>
       </c>
       <c r="J9" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K9" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06231218768826685</v>
+        <v>0.06687163759360548</v>
       </c>
       <c r="M9" t="n">
-        <v>6.648903010581512</v>
+        <v>6.677699372693308</v>
       </c>
       <c r="N9" t="n">
-        <v>67.84524123979514</v>
+        <v>68.02273003825375</v>
       </c>
       <c r="O9" t="n">
-        <v>8.23682227802659</v>
+        <v>8.247589347091292</v>
       </c>
       <c r="P9" t="n">
-        <v>386.6895849392336</v>
+        <v>386.8122907620261</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26782,7 +26920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J529"/>
+  <dimension ref="A1:J532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54281,6 +54419,162 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-45.76168442077477,170.6661740788254</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-45.762051652715606,170.66688152667788</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-45.76221835883712,170.66770225349038</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-45.76235718927375,170.66855746789344</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-45.76246139218691,170.66944714462616</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-45.762511357805714,170.67034341009017</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-45.762574166333465,170.671208180497</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-45.762554541006935,170.672089555412</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-45.76167765135519,170.66617916218743</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-45.76205214899103,170.66688122319243</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-45.762221147961334,170.66770123337227</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-45.76235736642351,170.66855742278165</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-45.762461039462686,170.6694472466749</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-45.76250790724244,170.6703443201624</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-45.762570583106765,170.67120865887716</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-45.762559304860474,170.67208925603177</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-45.76167765135519,170.66617916218743</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-45.76205024660188,170.6668823865533</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-45.762222978324075,170.6677005639197</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-45.76235922649581,170.66855694910765</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-45.76245830584998,170.6694480375527</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-45.762506226198774,170.6703447635309</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-45.76256816442871,170.67120898178374</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-45.76255570949931,170.6720894819791</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0501/nzd0501.xlsx
+++ b/data/nzd0501/nzd0501.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J532"/>
+  <dimension ref="A1:J534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19588,6 +19588,78 @@
         <v>368.93</v>
       </c>
       <c r="J532" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="C533" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="D533" t="n">
+        <v>361.1</v>
+      </c>
+      <c r="E533" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="F533" t="n">
+        <v>356.15</v>
+      </c>
+      <c r="G533" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="H533" t="n">
+        <v>365.88</v>
+      </c>
+      <c r="I533" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>377.45</v>
+      </c>
+      <c r="C534" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="D534" t="n">
+        <v>362.46</v>
+      </c>
+      <c r="E534" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="F534" t="n">
+        <v>357.22</v>
+      </c>
+      <c r="G534" t="n">
+        <v>365.86</v>
+      </c>
+      <c r="H534" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="I534" t="n">
+        <v>369.81</v>
+      </c>
+      <c r="J534" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -19604,7 +19676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B654"/>
+  <dimension ref="A1:B656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26147,6 +26219,26 @@
       </c>
       <c r="B654" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -26315,28 +26407,28 @@
         <v>0.0823</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3086318141584496</v>
+        <v>-0.3066690475103286</v>
       </c>
       <c r="J2" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K2" t="n">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05799787778684773</v>
+        <v>0.05767348447748533</v>
       </c>
       <c r="M2" t="n">
-        <v>7.404630851030439</v>
+        <v>7.387671040411182</v>
       </c>
       <c r="N2" t="n">
-        <v>83.05255138840413</v>
+        <v>82.78579487092841</v>
       </c>
       <c r="O2" t="n">
-        <v>9.113317254897041</v>
+        <v>9.09866995065369</v>
       </c>
       <c r="P2" t="n">
-        <v>380.9097182835694</v>
+        <v>380.887035959111</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26393,28 +26485,28 @@
         <v>0.0578</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4009600699011798</v>
+        <v>-0.4098784615106839</v>
       </c>
       <c r="J3" t="n">
+        <v>533</v>
+      </c>
+      <c r="K3" t="n">
         <v>531</v>
       </c>
-      <c r="K3" t="n">
-        <v>529</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.07760080992450691</v>
+        <v>0.08093617156333355</v>
       </c>
       <c r="M3" t="n">
-        <v>8.241406581912658</v>
+        <v>8.256512199601961</v>
       </c>
       <c r="N3" t="n">
-        <v>101.7721962750595</v>
+        <v>101.9659165756301</v>
       </c>
       <c r="O3" t="n">
-        <v>10.08822066942727</v>
+        <v>10.09781741643362</v>
       </c>
       <c r="P3" t="n">
-        <v>384.2844094636377</v>
+        <v>384.3878522338267</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26471,28 +26563,28 @@
         <v>0.1247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3308702991059165</v>
+        <v>-0.3399934583373059</v>
       </c>
       <c r="J4" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K4" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07020974868871743</v>
+        <v>0.0738090180248272</v>
       </c>
       <c r="M4" t="n">
-        <v>7.452695289735246</v>
+        <v>7.472431820346521</v>
       </c>
       <c r="N4" t="n">
-        <v>78.44778725768465</v>
+        <v>78.76986785783897</v>
       </c>
       <c r="O4" t="n">
-        <v>8.857075547701095</v>
+        <v>8.875239031025529</v>
       </c>
       <c r="P4" t="n">
-        <v>383.5943039324908</v>
+        <v>383.6990838569171</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26549,28 +26641,28 @@
         <v>0.1284</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4081594596218151</v>
+        <v>-0.4152720622110549</v>
       </c>
       <c r="J5" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K5" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L5" t="n">
-        <v>0.110468107927064</v>
+        <v>0.114127227178617</v>
       </c>
       <c r="M5" t="n">
-        <v>7.10841551002702</v>
+        <v>7.119998874040278</v>
       </c>
       <c r="N5" t="n">
-        <v>72.58751027218324</v>
+        <v>72.69012091686969</v>
       </c>
       <c r="O5" t="n">
-        <v>8.519830413346456</v>
+        <v>8.525850158011792</v>
       </c>
       <c r="P5" t="n">
-        <v>377.938321618187</v>
+        <v>378.0200093961894</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26627,28 +26719,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3947118192709023</v>
+        <v>-0.4008951239044052</v>
       </c>
       <c r="J6" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K6" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1498612922848476</v>
+        <v>0.1540471119249093</v>
       </c>
       <c r="M6" t="n">
-        <v>5.855925707018542</v>
+        <v>5.870945299342329</v>
       </c>
       <c r="N6" t="n">
-        <v>47.82314570337383</v>
+        <v>47.92719795328185</v>
       </c>
       <c r="O6" t="n">
-        <v>6.915428092560418</v>
+        <v>6.922947201393483</v>
       </c>
       <c r="P6" t="n">
-        <v>376.0788413029807</v>
+        <v>376.149855863298</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26705,28 +26797,28 @@
         <v>0.0723</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4580995249923026</v>
+        <v>-0.4626501182412491</v>
       </c>
       <c r="J7" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K7" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1858873330477346</v>
+        <v>0.1895457563457926</v>
       </c>
       <c r="M7" t="n">
-        <v>5.819278971883649</v>
+        <v>5.823400145403054</v>
       </c>
       <c r="N7" t="n">
-        <v>49.7315458034011</v>
+        <v>49.6990015734326</v>
       </c>
       <c r="O7" t="n">
-        <v>7.052059685184259</v>
+        <v>7.049751880274411</v>
       </c>
       <c r="P7" t="n">
-        <v>384.1413241788422</v>
+        <v>384.1935855652976</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26783,28 +26875,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3231619373083853</v>
+        <v>-0.3291094946337419</v>
       </c>
       <c r="J8" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K8" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07683119514958681</v>
+        <v>0.07971229629131582</v>
       </c>
       <c r="M8" t="n">
-        <v>6.820268416763935</v>
+        <v>6.828617633374667</v>
       </c>
       <c r="N8" t="n">
-        <v>67.89870604064454</v>
+        <v>67.90581978405015</v>
       </c>
       <c r="O8" t="n">
-        <v>8.240067113843462</v>
+        <v>8.24049875820937</v>
       </c>
       <c r="P8" t="n">
-        <v>383.4169218166301</v>
+        <v>383.4852301247755</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26861,28 +26953,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3001501282153313</v>
+        <v>-0.3068985627034478</v>
       </c>
       <c r="J9" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K9" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06687163759360548</v>
+        <v>0.06985341764654973</v>
       </c>
       <c r="M9" t="n">
-        <v>6.677699372693308</v>
+        <v>6.694586865615635</v>
       </c>
       <c r="N9" t="n">
-        <v>68.02273003825375</v>
+        <v>68.10536401661018</v>
       </c>
       <c r="O9" t="n">
-        <v>8.247589347091292</v>
+        <v>8.252597410307265</v>
       </c>
       <c r="P9" t="n">
-        <v>386.8122907620261</v>
+        <v>386.8897953140508</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26920,7 +27012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J532"/>
+  <dimension ref="A1:J534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54575,6 +54667,110 @@
         </is>
       </c>
     </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-45.76167765135519,170.66617916218743</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-45.7620525625539,170.66688097028788</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-45.76222132228159,170.66770116961487</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-45.76235754357325,170.66855737766983</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-45.762457247677325,170.66944834369895</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-45.76250613772279,170.67034478686605</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-45.76256932897739,170.6712088263102</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-45.76255912509241,170.67208926732914</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-45.76164348569242,170.66620481819538</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-45.76203783971573,170.66688997368763</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-45.762209468503634,170.66770550511617</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-45.76234709173835,170.66856003926597</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-45.76244781230437,170.66945107350216</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-45.76249684774464,170.67034723705976</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-45.76256198336259,170.67120980698925</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-45.762547799704734,170.67208997906312</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
